--- a/data/trans_camb/P6905-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-42,83; -16,71</t>
+          <t>-43,45; -15,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 21,52</t>
+          <t>-30,33; 18,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,18; -16,1</t>
+          <t>-44,52; -16,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 15,57</t>
+          <t>-56,92; 19,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 18,79</t>
+          <t>-53,6; 17,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,33; 27,05</t>
+          <t>-53,07; 23,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 0,35</t>
+          <t>-38,29; 1,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 12,33</t>
+          <t>-27,38; 13,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 25,56</t>
+          <t>-32,63; 22,0</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,59; 118,67</t>
+          <t>-84,92; 112,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-85,94; 33,55</t>
+          <t>-85,68; 49,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,59; 47,19</t>
+          <t>-75,13; 42,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,17; 58,86</t>
+          <t>-79,47; 54,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-88,36; 12,45</t>
+          <t>-88,54; 11,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 39,74</t>
+          <t>-65,04; 48,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-77,58; 77,36</t>
+          <t>-80,44; 78,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 10,33</t>
+          <t>-17,11; 10,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 3,94</t>
+          <t>-22,08; 4,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 30,11</t>
+          <t>-10,76; 28,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 9,87</t>
+          <t>-24,87; 8,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 20,4</t>
+          <t>-18,66; 18,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 19,86</t>
+          <t>-18,56; 18,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 6,26</t>
+          <t>-15,12; 6,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 5,22</t>
+          <t>-15,63; 6,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 17,75</t>
+          <t>-6,71; 19,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,29; 35,81</t>
+          <t>-41,83; 35,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 15,44</t>
+          <t>-55,59; 18,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 105,07</t>
+          <t>-28,19; 93,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 28,81</t>
+          <t>-47,57; 24,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 56,18</t>
+          <t>-35,26; 48,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 55,95</t>
+          <t>-36,04; 49,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 18,83</t>
+          <t>-35,02; 18,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 15,44</t>
+          <t>-37,37; 18,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 51,1</t>
+          <t>-16,59; 58,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 12,39</t>
+          <t>-11,93; 11,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 15,56</t>
+          <t>-9,38; 14,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 5,55</t>
+          <t>-19,13; 5,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 30,06</t>
+          <t>-4,72; 30,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 15,47</t>
+          <t>-15,69; 18,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 7,88</t>
+          <t>-21,19; 8,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 17,05</t>
+          <t>-3,26; 16,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 11,52</t>
+          <t>-8,25; 10,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 2,98</t>
+          <t>-15,07; 3,54</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-34,59; 56,5</t>
+          <t>-36,63; 54,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 73,98</t>
+          <t>-29,7; 71,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,61; 28,02</t>
+          <t>-58,4; 26,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 109,52</t>
+          <t>-9,48; 110,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,21; 55,23</t>
+          <t>-36,19; 66,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 28,43</t>
+          <t>-46,61; 31,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 68,05</t>
+          <t>-9,85; 67,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 44,92</t>
+          <t>-23,05; 43,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 12,04</t>
+          <t>-42,81; 14,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 9,85</t>
+          <t>-17,79; 8,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 12,9</t>
+          <t>-13,38; 13,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 1,57</t>
+          <t>-22,41; 1,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 22,78</t>
+          <t>-20,27; 23,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 26,47</t>
+          <t>-14,54; 26,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 12,96</t>
+          <t>-29,01; 12,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 9,51</t>
+          <t>-13,61; 9,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 14,01</t>
+          <t>-8,94; 13,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 5,95</t>
+          <t>-17,13; 4,06</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,49; 43,83</t>
+          <t>-50,2; 42,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 59,42</t>
+          <t>-36,18; 62,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,43; 8,35</t>
+          <t>-62,04; 7,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,56; 113,68</t>
+          <t>-49,11; 108,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 118,44</t>
+          <t>-31,71; 130,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 52,78</t>
+          <t>-59,94; 54,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 37,46</t>
+          <t>-38,53; 40,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 57,78</t>
+          <t>-24,71; 53,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 22,57</t>
+          <t>-49,38; 16,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 11,27</t>
+          <t>-23,82; 12,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 17,06</t>
+          <t>-21,79; 16,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 8,51</t>
+          <t>-23,7; 6,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 33,39</t>
+          <t>-32,15; 33,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 47,45</t>
+          <t>-19,11; 44,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 17,15</t>
+          <t>-34,7; 18,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 13,94</t>
+          <t>-18,71; 13,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 23,54</t>
+          <t>-10,56; 23,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 6,73</t>
+          <t>-19,37; 6,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,1; 74,53</t>
+          <t>-68,31; 71,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-59,01; 97,16</t>
+          <t>-59,24; 85,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 55,83</t>
+          <t>-62,64; 39,64</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-60,14; 224,87</t>
+          <t>-61,86; 207,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 292,06</t>
+          <t>-37,24; 271,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-58,0; 124,52</t>
+          <t>-60,25; 134,62</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,51; 66,04</t>
+          <t>-46,41; 68,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 108,09</t>
+          <t>-29,02; 112,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 34,5</t>
+          <t>-49,13; 28,97</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 2,25</t>
+          <t>-9,85; 2,63</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 3,71</t>
+          <t>-9,14; 4,05</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -0,03</t>
+          <t>-13,78; -0,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 10,02</t>
+          <t>-9,5; 9,37</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 9,98</t>
+          <t>-9,64; 9,53</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -0,22</t>
+          <t>-19,53; 0,2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 4,73</t>
+          <t>-6,75; 3,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,86</t>
+          <t>-6,1; 4,9</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -1,23</t>
+          <t>-11,74; -0,66</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 9,38</t>
+          <t>-30,45; 10,02</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 13,67</t>
+          <t>-28,7; 15,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 0,23</t>
+          <t>-41,48; -0,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 27,22</t>
+          <t>-21,26; 25,63</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 27,17</t>
+          <t>-20,72; 26,01</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -1,26</t>
+          <t>-43,83; 0,0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 15,97</t>
+          <t>-18,98; 11,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 12,36</t>
+          <t>-16,91; 15,67</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-32,56; -3,69</t>
+          <t>-32,19; -2,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6905-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,36</t>
+          <t>-14,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,53</t>
+          <t>-9,74</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-43,45; -15,64</t>
+          <t>-43,45; -16,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,33; 18,58</t>
+          <t>-28,86; 17,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-44,52; -16,54</t>
+          <t>-42,96; -16,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 19,37</t>
+          <t>-62,92; 9,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,6; 17,79</t>
+          <t>-50,75; 17,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,07; 23,5</t>
+          <t>-50,0; 29,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 1,2</t>
+          <t>-38,23; -0,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 13,46</t>
+          <t>-27,69; 12,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 22,0</t>
+          <t>-34,17; 18,8</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-28,47%</t>
+          <t>-24,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-20,31%</t>
+          <t>-26,25%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,92; 112,92</t>
+          <t>-83,53; 99,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-85,68; 49,48</t>
+          <t>-91,35; 29,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,13; 42,96</t>
+          <t>-74,82; 40,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,47; 54,48</t>
+          <t>-78,37; 71,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-88,54; 11,13</t>
+          <t>-88,33; 8,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,04; 48,16</t>
+          <t>-65,34; 50,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,44; 78,71</t>
+          <t>-81,55; 61,44</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,08</t>
+          <t>11,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>-1,28</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>6,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 10,11</t>
+          <t>-16,6; 10,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 4,02</t>
+          <t>-21,92; 4,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 28,26</t>
+          <t>-7,2; 30,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 8,47</t>
+          <t>-24,67; 9,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 18,26</t>
+          <t>-16,12; 18,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 18,73</t>
+          <t>-18,8; 17,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 6,11</t>
+          <t>-13,72; 7,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 6,2</t>
+          <t>-15,45; 5,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 19,21</t>
+          <t>-5,64; 20,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>-2,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,83; 35,8</t>
+          <t>-41,9; 36,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 18,69</t>
+          <t>-55,65; 19,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 93,74</t>
+          <t>-19,24; 101,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 24,29</t>
+          <t>-47,45; 27,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 48,75</t>
+          <t>-32,36; 49,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 49,61</t>
+          <t>-37,54; 46,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 18,23</t>
+          <t>-31,83; 20,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 18,74</t>
+          <t>-36,49; 19,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 58,84</t>
+          <t>-13,01; 61,28</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,57</t>
+          <t>-5,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,36</t>
+          <t>-7,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,64</t>
+          <t>-5,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 11,65</t>
+          <t>-12,06; 12,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 14,14</t>
+          <t>-9,64; 14,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 5,68</t>
+          <t>-17,58; 7,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 30,19</t>
+          <t>-3,56; 29,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 18,35</t>
+          <t>-16,43; 16,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 8,88</t>
+          <t>-23,13; 4,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 16,4</t>
+          <t>-3,54; 16,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 10,73</t>
+          <t>-9,2; 10,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 3,54</t>
+          <t>-14,14; 3,5</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-24,65%</t>
+          <t>-19,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-17,42%</t>
+          <t>-21,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-18,71%</t>
+          <t>-18,66%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 54,96</t>
+          <t>-36,5; 56,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 71,47</t>
+          <t>-30,22; 67,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,4; 26,89</t>
+          <t>-53,25; 33,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 110,76</t>
+          <t>-9,39; 105,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 66,69</t>
+          <t>-37,99; 59,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 31,58</t>
+          <t>-49,98; 21,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 67,07</t>
+          <t>-9,79; 69,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 43,56</t>
+          <t>-25,22; 40,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,81; 14,38</t>
+          <t>-40,76; 13,59</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,5</t>
+          <t>-7,91</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,13</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,22</t>
+          <t>-2,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 8,63</t>
+          <t>-18,45; 7,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 13,66</t>
+          <t>-12,61; 12,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 1,28</t>
+          <t>-19,91; 3,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 23,07</t>
+          <t>-21,8; 23,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 26,27</t>
+          <t>-17,17; 24,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 12,79</t>
+          <t>-20,09; 16,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 9,46</t>
+          <t>-13,77; 9,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 13,16</t>
+          <t>-7,34; 14,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 4,06</t>
+          <t>-12,19; 7,76</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-36,05%</t>
+          <t>-27,17%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-12,26%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-17,25%</t>
+          <t>-8,03%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,2; 42,44</t>
+          <t>-53,04; 37,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 62,35</t>
+          <t>-35,48; 52,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,04; 7,46</t>
+          <t>-56,08; 15,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 108,3</t>
+          <t>-51,71; 115,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 130,07</t>
+          <t>-38,1; 115,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,94; 54,82</t>
+          <t>-38,75; 75,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 40,08</t>
+          <t>-38,52; 38,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 53,83</t>
+          <t>-22,08; 59,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 16,24</t>
+          <t>-32,96; 34,51</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,72</t>
+          <t>-5,78</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-7,57</t>
+          <t>-7,59</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,83</t>
+          <t>-4,71</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 12,23</t>
+          <t>-24,2; 11,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 16,2</t>
+          <t>-20,55; 18,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 6,69</t>
+          <t>-21,55; 9,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 33,76</t>
+          <t>-25,47; 38,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 44,95</t>
+          <t>-17,91; 45,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 18,01</t>
+          <t>-36,81; 15,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 13,81</t>
+          <t>-15,53; 14,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 23,43</t>
+          <t>-9,75; 23,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 6,6</t>
+          <t>-18,32; 7,35</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-27,83%</t>
+          <t>-20,84%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-21,01%</t>
+          <t>-21,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-19,67%</t>
+          <t>-15,89%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,31; 71,47</t>
+          <t>-68,17; 68,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-59,24; 85,41</t>
+          <t>-55,5; 100,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,64; 39,64</t>
+          <t>-58,7; 55,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-61,86; 207,09</t>
+          <t>-50,45; 274,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,24; 271,4</t>
+          <t>-30,98; 268,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,25; 134,62</t>
+          <t>-61,65; 107,95</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,41; 68,94</t>
+          <t>-42,77; 64,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 112,79</t>
+          <t>-25,89; 105,36</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 28,97</t>
+          <t>-45,18; 37,61</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-7,2</t>
+          <t>-4,81</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-8,66</t>
+          <t>-7,38</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-4,34</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 2,63</t>
+          <t>-10,93; 2,39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 4,05</t>
+          <t>-9,49; 3,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -0,2</t>
+          <t>-11,83; 2,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 9,37</t>
+          <t>-10,16; 9,7</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 9,53</t>
+          <t>-7,8; 11,88</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 0,2</t>
+          <t>-15,28; 1,32</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 3,8</t>
+          <t>-7,24; 4,38</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 4,9</t>
+          <t>-6,47; 3,96</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,74; -0,66</t>
+          <t>-8,89; 0,72</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-23,97%</t>
+          <t>-16,02%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-21,15%</t>
+          <t>-18,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-17,44%</t>
+          <t>-12,94%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 10,02</t>
+          <t>-33,63; 8,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 15,23</t>
+          <t>-28,6; 12,35</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-41,48; -0,59</t>
+          <t>-35,7; 7,53</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 25,63</t>
+          <t>-22,32; 26,44</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 26,01</t>
+          <t>-17,72; 32,49</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 0,0</t>
+          <t>-33,19; 4,13</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 11,39</t>
+          <t>-19,6; 14,44</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 15,67</t>
+          <t>-18,03; 12,94</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-32,19; -2,0</t>
+          <t>-24,79; 2,47</t>
         </is>
       </c>
     </row>
